--- a/model_inference/latency_energy.xlsx
+++ b/model_inference/latency_energy.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gkgon\Desktop\资料\海思项目\高层次仿真器\model_inference\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB685A7B-DD74-42B7-8F9A-47EE60228B47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="延迟数据" sheetId="1" r:id="rId1"/>
     <sheet name="汇总数据" sheetId="2" r:id="rId2"/>
     <sheet name="能耗总计" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="51">
   <si>
     <t>模型</t>
   </si>
@@ -44,7 +33,7 @@
     <t>算子占总延时比例</t>
   </si>
   <si>
-    <t>seedoss</t>
+    <t>deepseek671b</t>
   </si>
   <si>
     <t>prefill</t>
@@ -53,40 +42,67 @@
     <t>decode</t>
   </si>
   <si>
-    <t>attn_rmsnorm</t>
-  </si>
-  <si>
-    <t>Q_proj</t>
-  </si>
-  <si>
-    <t>Q_rope</t>
-  </si>
-  <si>
-    <t>K_proj</t>
-  </si>
-  <si>
-    <t>K_rope</t>
-  </si>
-  <si>
-    <t>V_proj</t>
-  </si>
-  <si>
-    <t>QKT</t>
+    <t>mla rmsnorm</t>
+  </si>
+  <si>
+    <t>linear(q_a)</t>
+  </si>
+  <si>
+    <t>rmsnorm(q)</t>
+  </si>
+  <si>
+    <t>linear(q_b)</t>
+  </si>
+  <si>
+    <t>rope_q</t>
+  </si>
+  <si>
+    <t>linear(kv_a)</t>
+  </si>
+  <si>
+    <t>rmsnorm(kv)</t>
+  </si>
+  <si>
+    <t>rope_k</t>
+  </si>
+  <si>
+    <t>qkt_rope</t>
+  </si>
+  <si>
+    <t>q_absorb</t>
+  </si>
+  <si>
+    <t>q_absorb @ ctkv</t>
+  </si>
+  <si>
+    <t>rope_add_nope</t>
   </si>
   <si>
     <t>softmax</t>
   </si>
   <si>
-    <t>SV</t>
-  </si>
-  <si>
-    <t>O_proj</t>
-  </si>
-  <si>
-    <t>attn_resadd</t>
-  </si>
-  <si>
-    <t>ffn_rmsnorm</t>
+    <t>s_ctkv</t>
+  </si>
+  <si>
+    <t>sv_Wuv</t>
+  </si>
+  <si>
+    <t>linear_o</t>
+  </si>
+  <si>
+    <t>mla_resadd</t>
+  </si>
+  <si>
+    <t>rmsnorm_moe</t>
+  </si>
+  <si>
+    <t>router</t>
+  </si>
+  <si>
+    <t>sigmoid</t>
+  </si>
+  <si>
+    <t>rank_add</t>
   </si>
   <si>
     <t>linear_up</t>
@@ -104,7 +120,10 @@
     <t>linear_down</t>
   </si>
   <si>
-    <t>ffn_resadd</t>
+    <t>mul</t>
+  </si>
+  <si>
+    <t>moe_add</t>
   </si>
   <si>
     <t>汇总</t>
@@ -134,7 +153,7 @@
     <t>MAC功耗(W)</t>
   </si>
   <si>
-    <t>逐元素功耗(W)</t>
+    <t>Vector功耗(W)</t>
   </si>
   <si>
     <t>NoC功耗(W)</t>
@@ -155,12 +174,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00%"/>
+  </numFmts>
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -168,15 +190,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -223,7 +238,7 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -232,23 +247,15 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -290,7 +297,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -322,27 +329,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -374,24 +363,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -567,18 +538,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E61"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="3" width="30.6640625" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -595,7 +566,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -606,13 +577,13 @@
         <v>8</v>
       </c>
       <c r="D2">
-        <v>129.36967999999999</v>
+        <v>181.093968</v>
       </c>
       <c r="E2" s="1">
-        <v>1.1482624002683749E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.008978579326120029</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -623,13 +594,13 @@
         <v>9</v>
       </c>
       <c r="D3">
-        <v>576.97023999999999</v>
+        <v>146.84928</v>
       </c>
       <c r="E3" s="1">
-        <v>5.1210858113417343E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.007280738966764545</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -640,13 +611,13 @@
         <v>10</v>
       </c>
       <c r="D4">
-        <v>266.41023999999999</v>
+        <v>38.831696</v>
       </c>
       <c r="E4" s="1">
-        <v>2.3646101747988701E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.001925262706175712</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -657,13 +628,13 @@
         <v>11</v>
       </c>
       <c r="D5">
-        <v>78.691839999999999</v>
+        <v>1013.509376</v>
       </c>
       <c r="E5" s="1">
-        <v>6.984548549546922E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.05024946126412345</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -674,13 +645,13 @@
         <v>12</v>
       </c>
       <c r="D6">
-        <v>26.646784</v>
+        <v>217.061632</v>
       </c>
       <c r="E6" s="1">
-        <v>2.3651214222121398E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.01076184426843568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -691,13 +662,13 @@
         <v>13</v>
       </c>
       <c r="D7">
-        <v>78.691839999999999</v>
+        <v>73.42848000000001</v>
       </c>
       <c r="E7" s="1">
-        <v>6.984548549546922E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.003640559869318332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -708,13 +679,13 @@
         <v>14</v>
       </c>
       <c r="D8">
-        <v>157.33503999999999</v>
+        <v>12.969552</v>
       </c>
       <c r="E8" s="1">
-        <v>1.396477989871513E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.0006430261192147422</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -725,13 +696,13 @@
         <v>15</v>
       </c>
       <c r="D9">
-        <v>3009.4335999999998</v>
+        <v>1.702144</v>
       </c>
       <c r="E9" s="1">
-        <v>0.26711200406341717</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>8.439173925704281E-05</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -742,13 +713,13 @@
         <v>16</v>
       </c>
       <c r="D10">
-        <v>671.12064000000009</v>
+        <v>251.70688</v>
       </c>
       <c r="E10" s="1">
-        <v>5.9567481109642398E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.01247954426074631</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -759,13 +730,13 @@
         <v>17</v>
       </c>
       <c r="D11">
-        <v>576.84735999999998</v>
+        <v>1778.416896</v>
       </c>
       <c r="E11" s="1">
-        <v>5.1199951501934272E-2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.08817332433539785</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -776,13 +747,13 @@
         <v>18</v>
       </c>
       <c r="D12">
-        <v>1.7638400000000001</v>
+        <v>1006.6816</v>
       </c>
       <c r="E12" s="1">
-        <v>1.565553189966437E-4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.04991094237741499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -793,13 +764,13 @@
         <v>19</v>
       </c>
       <c r="D13">
-        <v>129.36967999999999</v>
+        <v>47.18848</v>
       </c>
       <c r="E13" s="1">
-        <v>1.1482624002683749E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.002339589306249165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -810,13 +781,13 @@
         <v>20</v>
       </c>
       <c r="D14">
-        <v>1521.0777599999999</v>
+        <v>4815.081472</v>
       </c>
       <c r="E14" s="1">
-        <v>0.13500817190646561</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.2387301544913015</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -827,13 +798,13 @@
         <v>21</v>
       </c>
       <c r="D15">
-        <v>1521.0777599999999</v>
+        <v>2952.822016</v>
       </c>
       <c r="E15" s="1">
-        <v>0.13500817190646561</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.1463999436279936</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -844,13 +815,13 @@
         <v>22</v>
       </c>
       <c r="D16">
-        <v>273.79968000000002</v>
+        <v>738.2295040000001</v>
       </c>
       <c r="E16" s="1">
-        <v>2.4301975373944889E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.03660117581909876</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -861,13 +832,13 @@
         <v>23</v>
       </c>
       <c r="D17">
-        <v>688.92492800000014</v>
+        <v>1258.46272</v>
       </c>
       <c r="E17" s="1">
-        <v>6.1147758225111003E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.06239416743292511</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -878,13 +849,13 @@
         <v>24</v>
       </c>
       <c r="D18">
-        <v>1557.2659200000001</v>
+        <v>2.46016</v>
       </c>
       <c r="E18" s="1">
-        <v>0.1382201689882312</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.0001219739230350701</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -895,13 +866,13 @@
         <v>25</v>
       </c>
       <c r="D19">
-        <v>1.7638400000000001</v>
+        <v>181.093968</v>
       </c>
       <c r="E19" s="1">
-        <v>1.565553189966437E-4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.008978579326120029</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -912,466 +883,801 @@
         <v>26</v>
       </c>
       <c r="D20">
-        <v>11371.426111999999</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36.72832</v>
+      </c>
+      <c r="E20" s="1">
+        <v>0.001820978016424715</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21">
+        <v>2.86976</v>
+      </c>
+      <c r="E21" s="1">
+        <v>0.0001422817562146864</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22">
+        <v>0.10496</v>
+      </c>
+      <c r="E22" s="1">
+        <v>5.203882252276665E-06</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
         <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23">
+        <v>1652.12928</v>
+      </c>
+      <c r="E23" s="1">
+        <v>0.08191202590185429</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" t="s">
+        <v>30</v>
+      </c>
+      <c r="D24">
+        <v>1652.12928</v>
+      </c>
+      <c r="E24" s="1">
+        <v>0.08191202590185429</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25">
+        <v>187.10784</v>
+      </c>
+      <c r="E25" s="1">
+        <v>0.009276745120406079</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26">
+        <v>459.493632</v>
+      </c>
+      <c r="E26" s="1">
+        <v>0.02278154303162105</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27">
+        <v>1417.12128</v>
+      </c>
+      <c r="E27" s="1">
+        <v>0.07026040661504945</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28">
+        <v>22.14144</v>
+      </c>
+      <c r="E28" s="1">
+        <v>0.001097765307315631</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29">
+        <v>22.14144</v>
+      </c>
+      <c r="E29" s="1">
+        <v>0.001097765307315631</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30">
+        <v>20316.365536</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" t="s">
         <v>8</v>
       </c>
-      <c r="D23">
-        <v>295.7312</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1.01657617566435E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" t="s">
+      <c r="D33">
+        <v>399.0159360000006</v>
+      </c>
+      <c r="E33" s="1">
+        <v>0.007368872026306497</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" t="s">
+        <v>5</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" t="s">
         <v>9</v>
       </c>
-      <c r="D24">
-        <v>1169.6537599999999</v>
-      </c>
-      <c r="E24" s="1">
-        <v>4.0206854947744022E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="D34">
+        <v>309.49376</v>
+      </c>
+      <c r="E34" s="1">
+        <v>0.005715611093739407</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" t="s">
+        <v>5</v>
+      </c>
+      <c r="B35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" t="s">
         <v>10</v>
       </c>
-      <c r="D25">
-        <v>545.91488000000004</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1.8765827242734699E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D35">
+        <v>114.6552320000043</v>
+      </c>
+      <c r="E35" s="1">
+        <v>0.002117408493064578</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" t="s">
+        <v>5</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" t="s">
         <v>11</v>
       </c>
-      <c r="D26">
-        <v>173.17887999999999</v>
-      </c>
-      <c r="E26" s="1">
-        <v>5.9530250286826481E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="D36">
+        <v>2050.588672000075</v>
+      </c>
+      <c r="E36" s="1">
+        <v>0.03786947873320608</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" t="s">
         <v>12</v>
       </c>
-      <c r="D27">
-        <v>66.387967999998054</v>
-      </c>
-      <c r="E27" s="1">
-        <v>2.2820867943445012E-3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="D37">
+        <v>447.2176639999929</v>
+      </c>
+      <c r="E37" s="1">
+        <v>0.008259042901784456</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" t="s">
+        <v>5</v>
+      </c>
+      <c r="B38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" t="s">
         <v>13</v>
       </c>
-      <c r="D28">
-        <v>173.17887999999999</v>
-      </c>
-      <c r="E28" s="1">
-        <v>5.9530250286826481E-3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="D38">
+        <v>162.69312</v>
+      </c>
+      <c r="E38" s="1">
+        <v>0.00300455363477143</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" t="s">
         <v>14</v>
       </c>
-      <c r="D29">
-        <v>517.44767999999999</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1.7787267073639521E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="D39">
+        <v>63.01286399999768</v>
+      </c>
+      <c r="E39" s="1">
+        <v>0.001163697208391792</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" t="s">
         <v>15</v>
       </c>
-      <c r="D30">
-        <v>11214.83776</v>
-      </c>
-      <c r="E30" s="1">
-        <v>0.38551011461614282</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>5</v>
-      </c>
-      <c r="B31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="D40">
+        <v>16.7444480000005</v>
+      </c>
+      <c r="E40" s="1">
+        <v>0.0003092299914135442</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" t="s">
         <v>16</v>
       </c>
-      <c r="D31">
-        <v>2258.04288</v>
-      </c>
-      <c r="E31" s="1">
-        <v>7.7620237412776016E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>5</v>
-      </c>
-      <c r="B32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="D41">
+        <v>818.3808</v>
+      </c>
+      <c r="E41" s="1">
+        <v>0.01511354018699224</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" t="s">
         <v>17</v>
       </c>
-      <c r="D32">
-        <v>1169.48992</v>
-      </c>
-      <c r="E32" s="1">
-        <v>4.0201222946770802E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="D42">
+        <v>3580.526591999943</v>
+      </c>
+      <c r="E42" s="1">
+        <v>0.06612378068838552</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" t="s">
         <v>18</v>
       </c>
-      <c r="D33">
-        <v>8.8473600000000001</v>
-      </c>
-      <c r="E33" s="1">
-        <v>3.0412805255332348E-4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="D43">
+        <v>3225.84576</v>
+      </c>
+      <c r="E43" s="1">
+        <v>0.05957367222055859</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" t="s">
         <v>19</v>
       </c>
-      <c r="D34">
-        <v>295.7312</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1.01657617566435E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>5</v>
-      </c>
-      <c r="B35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="D44">
+        <v>186.91584</v>
+      </c>
+      <c r="E44" s="1">
+        <v>0.003451889462002788</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" t="s">
         <v>20</v>
       </c>
-      <c r="D35">
-        <v>3057.90976</v>
-      </c>
-      <c r="E35" s="1">
-        <v>0.10511566616398579</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>5</v>
-      </c>
-      <c r="B36" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D45">
+        <v>17918.574592</v>
+      </c>
+      <c r="E45" s="1">
+        <v>0.3309133073378677</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" t="s">
         <v>21</v>
       </c>
-      <c r="D36">
-        <v>3057.90976</v>
-      </c>
-      <c r="E36" s="1">
-        <v>0.10511566616398579</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="D46">
+        <v>8784.084991999727</v>
+      </c>
+      <c r="E46" s="1">
+        <v>0.1622210852607286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" t="s">
         <v>22</v>
       </c>
-      <c r="D37">
-        <v>556.40063999999995</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1.9126275305020129E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>5</v>
-      </c>
-      <c r="B38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" t="s">
+      <c r="D47">
+        <v>1500.151807999942</v>
+      </c>
+      <c r="E47" s="1">
+        <v>0.02770422355558218</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" t="s">
         <v>23</v>
       </c>
-      <c r="D38">
-        <v>1391.0671360000331</v>
-      </c>
-      <c r="E38" s="1">
-        <v>4.7817941062940732E-2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="D48">
+        <v>2532.63872</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0.04677179263473994</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" t="s">
         <v>24</v>
       </c>
-      <c r="D39">
-        <v>3130.3270400000001</v>
-      </c>
-      <c r="E39" s="1">
-        <v>0.1076050105941444</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>5</v>
-      </c>
-      <c r="B40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="D49">
+        <v>10.15808</v>
+      </c>
+      <c r="E49" s="1">
+        <v>0.0001875954938125163</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" t="s">
         <v>25</v>
       </c>
-      <c r="D40">
-        <v>8.8473600000000001</v>
-      </c>
-      <c r="E40" s="1">
-        <v>3.0412805255332348E-4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="D50">
+        <v>399.0159360000006</v>
+      </c>
+      <c r="E50" s="1">
+        <v>0.007368872026306497</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" t="s">
         <v>26</v>
       </c>
-      <c r="D41">
-        <v>29316.675584000379</v>
+      <c r="D51">
+        <v>89.2928</v>
+      </c>
+      <c r="E51" s="1">
+        <v>0.001649024905287441</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" t="s">
+        <v>27</v>
+      </c>
+      <c r="D52">
+        <v>14.41792</v>
+      </c>
+      <c r="E52" s="1">
+        <v>0.0002662645718629263</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" t="s">
+        <v>28</v>
+      </c>
+      <c r="D53">
+        <v>5.57056</v>
+      </c>
+      <c r="E53" s="1">
+        <v>0.000102874948219767</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54">
+        <v>3446.04672</v>
+      </c>
+      <c r="E54" s="1">
+        <v>0.06364025840901055</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>30</v>
+      </c>
+      <c r="D55">
+        <v>3446.04672</v>
+      </c>
+      <c r="E55" s="1">
+        <v>0.06364025840901055</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56">
+        <v>432.04608</v>
+      </c>
+      <c r="E56" s="1">
+        <v>0.00797885995457428</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57">
+        <v>1037.205503999962</v>
+      </c>
+      <c r="E57" s="1">
+        <v>0.01915471021176568</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58">
+        <v>2975.66208</v>
+      </c>
+      <c r="E58" s="1">
+        <v>0.05495337675198259</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" t="s">
+        <v>34</v>
+      </c>
+      <c r="D59">
+        <v>91.42272</v>
+      </c>
+      <c r="E59" s="1">
+        <v>0.001688359444312647</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" t="s">
+        <v>35</v>
+      </c>
+      <c r="D60">
+        <v>91.42272</v>
+      </c>
+      <c r="E60" s="1">
+        <v>0.001688359444312647</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61">
+        <v>54458.50624</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.6640625" customWidth="1"/>
-    <col min="2" max="9" width="18.6640625" customWidth="1"/>
+    <col min="1" max="1" width="15.7109375" customWidth="1"/>
+    <col min="2" max="9" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2">
-        <v>11.371426112</v>
+        <v>20.316365536</v>
       </c>
       <c r="C2">
-        <v>40688.101696000384</v>
+        <v>74774.871776</v>
       </c>
       <c r="D2">
-        <v>12885.53602026455</v>
+        <v>7011.553313933963</v>
       </c>
       <c r="E2">
-        <v>69.857852543065945</v>
+        <v>37.6066135742764</v>
       </c>
       <c r="F2">
-        <v>7793.6270399999994</v>
+        <v>11661.82048</v>
       </c>
       <c r="G2">
-        <v>3577.7990719999998</v>
+        <v>8654.545056000001</v>
       </c>
       <c r="H2">
-        <v>18010.470399999998</v>
+        <v>30445.78816</v>
       </c>
       <c r="I2">
-        <v>11306.205183999669</v>
+        <v>24012.71808</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="7" width="18.6640625" customWidth="1"/>
+    <col min="1" max="7" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2">
-        <v>19.38207451042474</v>
+        <v>8.635463244614526</v>
       </c>
       <c r="B2">
-        <v>1.5306498807325699</v>
+        <v>1.143386881476615</v>
       </c>
       <c r="C2">
-        <v>0.22764682276202489</v>
+        <v>0.2614284734523799</v>
       </c>
       <c r="D2">
-        <v>1.3300347195828909E-2</v>
+        <v>0.01013217693350258</v>
       </c>
       <c r="E2">
-        <v>13.93712770740699</v>
+        <v>3.066437886819119</v>
       </c>
       <c r="F2">
-        <v>2.102043262057797E-2</v>
+        <v>0.02787176580928518</v>
       </c>
       <c r="G2">
-        <v>35.111819701142728</v>
+        <v>13.14472042910543</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>